--- a/artfynd/Björnideforsen B artfynd.xlsx
+++ b/artfynd/Björnideforsen B artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY148"/>
+  <dimension ref="A1:AY149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3796,10 +3796,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>479071</v>
+        <v>135058981</v>
       </c>
       <c r="B32" t="n">
-        <v>92083</v>
+        <v>92220</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3807,31 +3807,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Trollberget, Pi lm</t>
+          <t>Akkajaur, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>694274</v>
+        <v>694448</v>
       </c>
       <c r="R32" t="n">
         <v>7327659</v>
@@ -3861,12 +3861,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2007-09-08</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2007-09-08</t>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3881,19 +3886,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mariell Vikström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mariell Vikström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118713302</v>
+        <v>479071</v>
       </c>
       <c r="B33" t="n">
         <v>92083</v>
@@ -3924,14 +3929,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Trollberget, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>694401</v>
+        <v>694274</v>
       </c>
       <c r="R33" t="n">
-        <v>7327511</v>
+        <v>7327659</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3958,12 +3963,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2007-09-08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2007-09-08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3978,48 +3983,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Mariell Vikström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Mariell Vikström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118710623</v>
+        <v>118713302</v>
       </c>
       <c r="B34" t="n">
-        <v>93191</v>
+        <v>92083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>1503</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4029,13 +4030,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>694340</v>
+        <v>694401</v>
       </c>
       <c r="R34" t="n">
-        <v>7327606</v>
+        <v>7327511</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4079,12 +4080,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4095,10 +4096,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118710617</v>
+        <v>118710623</v>
       </c>
       <c r="B35" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4106,21 +4107,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4130,10 +4131,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>694404</v>
+        <v>694340</v>
       </c>
       <c r="R35" t="n">
-        <v>7327574</v>
+        <v>7327606</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4196,10 +4197,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134864200</v>
+        <v>118710617</v>
       </c>
       <c r="B36" t="n">
-        <v>93271</v>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4227,17 +4228,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>694400</v>
+        <v>694404</v>
       </c>
       <c r="R36" t="n">
-        <v>7327593</v>
+        <v>7327574</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4261,12 +4262,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4281,22 +4282,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134864196</v>
+        <v>134864200</v>
       </c>
       <c r="B37" t="n">
-        <v>78776</v>
+        <v>93271</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4304,21 +4309,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4328,10 +4333,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>694323</v>
+        <v>694400</v>
       </c>
       <c r="R37" t="n">
-        <v>7327578</v>
+        <v>7327593</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4374,21 +4379,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4405,10 +4395,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118710600</v>
+        <v>134864196</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>78776</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4416,37 +4406,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>694405</v>
+        <v>694323</v>
       </c>
       <c r="R38" t="n">
-        <v>7327511</v>
+        <v>7327578</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4470,12 +4460,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4486,30 +4476,41 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118710575</v>
+        <v>118710600</v>
       </c>
       <c r="B39" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4517,21 +4518,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4541,10 +4542,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>694532</v>
+        <v>694405</v>
       </c>
       <c r="R39" t="n">
-        <v>7327517</v>
+        <v>7327511</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4607,7 +4608,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118710577</v>
+        <v>118710575</v>
       </c>
       <c r="B40" t="n">
         <v>79946</v>
@@ -4642,10 +4643,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>694341</v>
+        <v>694532</v>
       </c>
       <c r="R40" t="n">
-        <v>7327604</v>
+        <v>7327517</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4708,10 +4709,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134864198</v>
+        <v>118710577</v>
       </c>
       <c r="B41" t="n">
-        <v>78377</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4719,37 +4720,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>694322</v>
+        <v>694341</v>
       </c>
       <c r="R41" t="n">
-        <v>7327579</v>
+        <v>7327604</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4773,12 +4774,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4789,41 +4790,30 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118710590</v>
+        <v>134864198</v>
       </c>
       <c r="B42" t="n">
-        <v>79085</v>
+        <v>78377</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4831,37 +4821,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>694416</v>
+        <v>694322</v>
       </c>
       <c r="R42" t="n">
-        <v>7327520</v>
+        <v>7327579</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4885,12 +4875,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4901,30 +4891,41 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134864199</v>
+        <v>118710590</v>
       </c>
       <c r="B43" t="n">
-        <v>79396</v>
+        <v>79085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4932,37 +4933,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>694311</v>
+        <v>694416</v>
       </c>
       <c r="R43" t="n">
-        <v>7327564</v>
+        <v>7327520</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4986,12 +4987,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5002,38 +5003,27 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134864201</v>
+        <v>134864199</v>
       </c>
       <c r="B44" t="n">
         <v>79396</v>
@@ -5068,10 +5058,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>694553</v>
+        <v>694311</v>
       </c>
       <c r="R44" t="n">
-        <v>7327555</v>
+        <v>7327564</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5145,10 +5135,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118710616</v>
+        <v>134864201</v>
       </c>
       <c r="B45" t="n">
-        <v>78993</v>
+        <v>79396</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5156,37 +5146,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>260591</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>694579</v>
+        <v>694553</v>
       </c>
       <c r="R45" t="n">
-        <v>7327263</v>
+        <v>7327555</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5210,12 +5200,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5226,27 +5216,38 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118713511</v>
+        <v>118710616</v>
       </c>
       <c r="B46" t="n">
         <v>78993</v>
@@ -5281,13 +5282,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>694605</v>
+        <v>694579</v>
       </c>
       <c r="R46" t="n">
-        <v>7327124</v>
+        <v>7327263</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5331,12 +5332,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5347,45 +5348,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118722921</v>
+        <v>118713511</v>
       </c>
       <c r="B47" t="n">
-        <v>92509</v>
+        <v>78993</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>760</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>694676</v>
+        <v>694605</v>
       </c>
       <c r="R47" t="n">
-        <v>7327049</v>
+        <v>7327124</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5432,12 +5433,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5448,48 +5449,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118710601</v>
+        <v>118722921</v>
       </c>
       <c r="B48" t="n">
-        <v>79406</v>
+        <v>92509</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>864</v>
+        <v>760</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>694828</v>
+        <v>694676</v>
       </c>
       <c r="R48" t="n">
-        <v>7327045</v>
+        <v>7327049</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5533,12 +5534,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5549,7 +5550,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118710604</v>
+        <v>118710601</v>
       </c>
       <c r="B49" t="n">
         <v>79406</v>
@@ -5578,19 +5579,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>694844</v>
+        <v>694828</v>
       </c>
       <c r="R49" t="n">
-        <v>7327214</v>
+        <v>7327045</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5631,7 +5629,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5654,7 +5651,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118710605</v>
+        <v>118710604</v>
       </c>
       <c r="B50" t="n">
         <v>79406</v>
@@ -5692,10 +5689,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>694712</v>
+        <v>694844</v>
       </c>
       <c r="R50" t="n">
-        <v>7327141</v>
+        <v>7327214</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5759,7 +5756,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118713506</v>
+        <v>118710605</v>
       </c>
       <c r="B51" t="n">
         <v>79406</v>
@@ -5788,19 +5785,22 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>694810</v>
+        <v>694712</v>
       </c>
       <c r="R51" t="n">
-        <v>7326940</v>
+        <v>7327141</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5838,18 +5838,19 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5860,10 +5861,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118710612</v>
+        <v>118713506</v>
       </c>
       <c r="B52" t="n">
-        <v>83173</v>
+        <v>79406</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5871,21 +5872,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5895,13 +5896,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>694901</v>
+        <v>694810</v>
       </c>
       <c r="R52" t="n">
-        <v>7327141</v>
+        <v>7326940</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5945,12 +5946,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5961,7 +5962,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118710613</v>
+        <v>118710612</v>
       </c>
       <c r="B53" t="n">
         <v>83173</v>
@@ -5996,10 +5997,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>694814</v>
+        <v>694901</v>
       </c>
       <c r="R53" t="n">
-        <v>7327052</v>
+        <v>7327141</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6062,7 +6063,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118713510</v>
+        <v>118710613</v>
       </c>
       <c r="B54" t="n">
         <v>83173</v>
@@ -6097,13 +6098,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>694805</v>
+        <v>694814</v>
       </c>
       <c r="R54" t="n">
-        <v>7326941</v>
+        <v>7327052</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6147,12 +6148,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6163,10 +6164,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118713297</v>
+        <v>118713510</v>
       </c>
       <c r="B55" t="n">
-        <v>92097</v>
+        <v>83173</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6174,21 +6175,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1588</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6198,10 +6199,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>694713</v>
+        <v>694805</v>
       </c>
       <c r="R55" t="n">
-        <v>7326945</v>
+        <v>7326941</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6264,10 +6265,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118713494</v>
+        <v>118713297</v>
       </c>
       <c r="B56" t="n">
-        <v>80433</v>
+        <v>92097</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6275,21 +6276,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>1588</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6299,10 +6300,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>694829</v>
+        <v>694713</v>
       </c>
       <c r="R56" t="n">
-        <v>7326976</v>
+        <v>7326945</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6365,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118708329</v>
+        <v>118713494</v>
       </c>
       <c r="B57" t="n">
-        <v>93197</v>
+        <v>80433</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6376,21 +6377,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6400,13 +6401,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>694646</v>
+        <v>694829</v>
       </c>
       <c r="R57" t="n">
-        <v>7327055</v>
+        <v>7326976</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6450,12 +6451,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6466,7 +6467,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118708330</v>
+        <v>118708329</v>
       </c>
       <c r="B58" t="n">
         <v>93197</v>
@@ -6501,10 +6502,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>694661</v>
+        <v>694646</v>
       </c>
       <c r="R58" t="n">
-        <v>7327056</v>
+        <v>7327055</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -6567,7 +6568,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118713512</v>
+        <v>118708330</v>
       </c>
       <c r="B59" t="n">
         <v>93197</v>
@@ -6602,13 +6603,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>694609</v>
+        <v>694661</v>
       </c>
       <c r="R59" t="n">
-        <v>7327059</v>
+        <v>7327056</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6652,12 +6653,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6668,7 +6669,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118734896</v>
+        <v>118713512</v>
       </c>
       <c r="B60" t="n">
         <v>93197</v>
@@ -6699,14 +6700,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>694794</v>
+        <v>694609</v>
       </c>
       <c r="R60" t="n">
-        <v>7327158</v>
+        <v>7327059</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6736,19 +6737,9 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>16:47</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6763,12 +6754,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6779,7 +6770,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118734897</v>
+        <v>118734896</v>
       </c>
       <c r="B61" t="n">
         <v>93197</v>
@@ -6814,10 +6805,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>694616</v>
+        <v>694794</v>
       </c>
       <c r="R61" t="n">
-        <v>7327269</v>
+        <v>7327158</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6849,7 +6840,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6859,7 +6850,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6890,48 +6881,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118710602</v>
+        <v>118734897</v>
       </c>
       <c r="B62" t="n">
-        <v>91282</v>
+        <v>93197</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>694778</v>
+        <v>694616</v>
       </c>
       <c r="R62" t="n">
-        <v>7327400</v>
+        <v>7327269</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6958,9 +6949,19 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6975,12 +6976,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6991,32 +6992,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118710606</v>
+        <v>118710602</v>
       </c>
       <c r="B63" t="n">
-        <v>79327</v>
+        <v>91282</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7026,10 +7027,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>694902</v>
+        <v>694778</v>
       </c>
       <c r="R63" t="n">
-        <v>7327141</v>
+        <v>7327400</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7092,7 +7093,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118710607</v>
+        <v>118710606</v>
       </c>
       <c r="B64" t="n">
         <v>79327</v>
@@ -7127,10 +7128,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>694879</v>
+        <v>694902</v>
       </c>
       <c r="R64" t="n">
-        <v>7327173</v>
+        <v>7327141</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7193,7 +7194,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118710608</v>
+        <v>118710607</v>
       </c>
       <c r="B65" t="n">
         <v>79327</v>
@@ -7228,10 +7229,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>694586</v>
+        <v>694879</v>
       </c>
       <c r="R65" t="n">
-        <v>7327268</v>
+        <v>7327173</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7294,7 +7295,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118710610</v>
+        <v>118710608</v>
       </c>
       <c r="B66" t="n">
         <v>79327</v>
@@ -7329,10 +7330,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>694613</v>
+        <v>694586</v>
       </c>
       <c r="R66" t="n">
-        <v>7327275</v>
+        <v>7327268</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7395,7 +7396,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118710611</v>
+        <v>118710610</v>
       </c>
       <c r="B67" t="n">
         <v>79327</v>
@@ -7430,10 +7431,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>694828</v>
+        <v>694613</v>
       </c>
       <c r="R67" t="n">
-        <v>7327045</v>
+        <v>7327275</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7496,7 +7497,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118713303</v>
+        <v>118710611</v>
       </c>
       <c r="B68" t="n">
         <v>79327</v>
@@ -7531,13 +7532,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>694709</v>
+        <v>694828</v>
       </c>
       <c r="R68" t="n">
-        <v>7326944</v>
+        <v>7327045</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7581,12 +7582,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7597,7 +7598,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118713507</v>
+        <v>118713303</v>
       </c>
       <c r="B69" t="n">
         <v>79327</v>
@@ -7632,10 +7633,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>694577</v>
+        <v>694709</v>
       </c>
       <c r="R69" t="n">
-        <v>7327264</v>
+        <v>7326944</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7698,7 +7699,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118713508</v>
+        <v>118713507</v>
       </c>
       <c r="B70" t="n">
         <v>79327</v>
@@ -7733,10 +7734,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>694807</v>
+        <v>694577</v>
       </c>
       <c r="R70" t="n">
-        <v>7326939</v>
+        <v>7327264</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7799,7 +7800,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118722906</v>
+        <v>118713508</v>
       </c>
       <c r="B71" t="n">
         <v>79327</v>
@@ -7830,14 +7831,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>694699</v>
+        <v>694807</v>
       </c>
       <c r="R71" t="n">
-        <v>7327045</v>
+        <v>7326939</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7884,12 +7885,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7900,7 +7901,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118722907</v>
+        <v>118722906</v>
       </c>
       <c r="B72" t="n">
         <v>79327</v>
@@ -7935,10 +7936,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>694749</v>
+        <v>694699</v>
       </c>
       <c r="R72" t="n">
-        <v>7327056</v>
+        <v>7327045</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8001,7 +8002,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118722908</v>
+        <v>118722907</v>
       </c>
       <c r="B73" t="n">
         <v>79327</v>
@@ -8036,10 +8037,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>694764</v>
+        <v>694749</v>
       </c>
       <c r="R73" t="n">
-        <v>7326998</v>
+        <v>7327056</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8102,7 +8103,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118722909</v>
+        <v>118722908</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8137,10 +8138,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>694808</v>
+        <v>694764</v>
       </c>
       <c r="R74" t="n">
-        <v>7326935</v>
+        <v>7326998</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8203,10 +8204,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134864193</v>
+        <v>118722909</v>
       </c>
       <c r="B75" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8234,14 +8235,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>694579</v>
+        <v>694808</v>
       </c>
       <c r="R75" t="n">
-        <v>7327260</v>
+        <v>7326935</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8268,12 +8269,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8284,38 +8285,27 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134864209</v>
+        <v>134864193</v>
       </c>
       <c r="B76" t="n">
         <v>79373</v>
@@ -8350,10 +8340,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>694765</v>
+        <v>694579</v>
       </c>
       <c r="R76" t="n">
-        <v>7327166</v>
+        <v>7327260</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8427,7 +8417,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134864211</v>
+        <v>134864209</v>
       </c>
       <c r="B77" t="n">
         <v>79373</v>
@@ -8462,10 +8452,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>694804</v>
+        <v>694765</v>
       </c>
       <c r="R77" t="n">
-        <v>7327057</v>
+        <v>7327166</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8539,48 +8529,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118708332</v>
+        <v>134864211</v>
       </c>
       <c r="B78" t="n">
-        <v>78730</v>
+        <v>79373</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>694666</v>
+        <v>694804</v>
       </c>
       <c r="R78" t="n">
-        <v>7327052</v>
+        <v>7327057</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8604,12 +8594,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8620,27 +8610,38 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118713520</v>
+        <v>118708332</v>
       </c>
       <c r="B79" t="n">
         <v>78730</v>
@@ -8675,13 +8676,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>694708</v>
+        <v>694666</v>
       </c>
       <c r="R79" t="n">
-        <v>7327047</v>
+        <v>7327052</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8725,12 +8726,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8741,10 +8742,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118710571</v>
+        <v>118713520</v>
       </c>
       <c r="B80" t="n">
-        <v>83307</v>
+        <v>78730</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8752,21 +8753,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8776,13 +8777,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>694710</v>
+        <v>694708</v>
       </c>
       <c r="R80" t="n">
-        <v>7327188</v>
+        <v>7327047</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8826,12 +8827,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8842,7 +8843,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118713483</v>
+        <v>118710571</v>
       </c>
       <c r="B81" t="n">
         <v>83307</v>
@@ -8877,13 +8878,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>694804</v>
+        <v>694710</v>
       </c>
       <c r="R81" t="n">
-        <v>7326934</v>
+        <v>7327188</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8927,12 +8928,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8943,7 +8944,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118722871</v>
+        <v>118713483</v>
       </c>
       <c r="B82" t="n">
         <v>83307</v>
@@ -8974,14 +8975,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>694807</v>
+        <v>694804</v>
       </c>
       <c r="R82" t="n">
-        <v>7326961</v>
+        <v>7326934</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9028,12 +9029,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9044,10 +9045,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134864210</v>
+        <v>118722871</v>
       </c>
       <c r="B83" t="n">
-        <v>83358</v>
+        <v>83307</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9075,14 +9076,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>694762</v>
+        <v>694807</v>
       </c>
       <c r="R83" t="n">
-        <v>7327178</v>
+        <v>7326961</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9109,12 +9110,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9125,41 +9126,30 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118710599</v>
+        <v>134864210</v>
       </c>
       <c r="B84" t="n">
-        <v>79084</v>
+        <v>83358</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9167,37 +9157,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>694671</v>
+        <v>694762</v>
       </c>
       <c r="R84" t="n">
-        <v>7327465</v>
+        <v>7327178</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9221,12 +9211,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9237,27 +9227,38 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118712794</v>
+        <v>118710599</v>
       </c>
       <c r="B85" t="n">
         <v>79084</v>
@@ -9288,17 +9289,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>694796</v>
+        <v>694671</v>
       </c>
       <c r="R85" t="n">
-        <v>7327132</v>
+        <v>7327465</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9342,12 +9343,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9358,7 +9359,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118713504</v>
+        <v>118712794</v>
       </c>
       <c r="B86" t="n">
         <v>79084</v>
@@ -9387,23 +9388,16 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>694577</v>
+        <v>694796</v>
       </c>
       <c r="R86" t="n">
-        <v>7327264</v>
+        <v>7327132</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9444,19 +9438,18 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9467,7 +9460,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118713505</v>
+        <v>118713504</v>
       </c>
       <c r="B87" t="n">
         <v>79084</v>
@@ -9512,7 +9505,7 @@
         <v>694577</v>
       </c>
       <c r="R87" t="n">
-        <v>7327172</v>
+        <v>7327264</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9576,10 +9569,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118708328</v>
+        <v>118713505</v>
       </c>
       <c r="B88" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9587,37 +9580,44 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>694666</v>
+        <v>694577</v>
       </c>
       <c r="R88" t="n">
-        <v>7327051</v>
+        <v>7327172</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9655,18 +9655,19 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9677,7 +9678,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118710572</v>
+        <v>118708328</v>
       </c>
       <c r="B89" t="n">
         <v>79946</v>
@@ -9712,13 +9713,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>694777</v>
+        <v>694666</v>
       </c>
       <c r="R89" t="n">
-        <v>7327389</v>
+        <v>7327051</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9762,12 +9763,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9778,7 +9779,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118710573</v>
+        <v>118710572</v>
       </c>
       <c r="B90" t="n">
         <v>79946</v>
@@ -9813,10 +9814,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>694670</v>
+        <v>694777</v>
       </c>
       <c r="R90" t="n">
-        <v>7327462</v>
+        <v>7327389</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9879,7 +9880,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118710579</v>
+        <v>118710573</v>
       </c>
       <c r="B91" t="n">
         <v>79946</v>
@@ -9914,10 +9915,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>694578</v>
+        <v>694670</v>
       </c>
       <c r="R91" t="n">
-        <v>7327260</v>
+        <v>7327462</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9980,7 +9981,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118710580</v>
+        <v>118710579</v>
       </c>
       <c r="B92" t="n">
         <v>79946</v>
@@ -10015,10 +10016,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>694680</v>
+        <v>694578</v>
       </c>
       <c r="R92" t="n">
-        <v>7327208</v>
+        <v>7327260</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10081,7 +10082,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118710581</v>
+        <v>118710580</v>
       </c>
       <c r="B93" t="n">
         <v>79946</v>
@@ -10116,10 +10117,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>694844</v>
+        <v>694680</v>
       </c>
       <c r="R93" t="n">
-        <v>7327030</v>
+        <v>7327208</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10182,7 +10183,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118712785</v>
+        <v>118710581</v>
       </c>
       <c r="B94" t="n">
         <v>79946</v>
@@ -10213,17 +10214,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>694796</v>
+        <v>694844</v>
       </c>
       <c r="R94" t="n">
-        <v>7327132</v>
+        <v>7327030</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10267,12 +10268,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10283,7 +10284,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118713484</v>
+        <v>118712785</v>
       </c>
       <c r="B95" t="n">
         <v>79946</v>
@@ -10314,14 +10315,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>694578</v>
+        <v>694796</v>
       </c>
       <c r="R95" t="n">
-        <v>7327177</v>
+        <v>7327132</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10368,12 +10369,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10384,7 +10385,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118713485</v>
+        <v>118713484</v>
       </c>
       <c r="B96" t="n">
         <v>79946</v>
@@ -10419,10 +10420,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>694605</v>
+        <v>694578</v>
       </c>
       <c r="R96" t="n">
-        <v>7327124</v>
+        <v>7327177</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10485,10 +10486,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134864194</v>
+        <v>118713485</v>
       </c>
       <c r="B97" t="n">
-        <v>79992</v>
+        <v>79946</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10516,14 +10517,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>694575</v>
+        <v>694605</v>
       </c>
       <c r="R97" t="n">
-        <v>7327264</v>
+        <v>7327124</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10550,12 +10551,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10566,76 +10567,65 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118722883</v>
+        <v>134864194</v>
       </c>
       <c r="B98" t="n">
-        <v>80336</v>
+        <v>79992</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>694664</v>
+        <v>694575</v>
       </c>
       <c r="R98" t="n">
-        <v>7327029</v>
+        <v>7327264</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10662,12 +10652,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10678,30 +10668,41 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118712788</v>
+        <v>118722883</v>
       </c>
       <c r="B99" t="n">
-        <v>80461</v>
+        <v>80336</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10709,21 +10710,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10733,10 +10734,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>694616</v>
+        <v>694664</v>
       </c>
       <c r="R99" t="n">
-        <v>7327016</v>
+        <v>7327029</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10783,12 +10784,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10799,10 +10800,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118710618</v>
+        <v>118712788</v>
       </c>
       <c r="B100" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10810,37 +10811,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>694712</v>
+        <v>694616</v>
       </c>
       <c r="R100" t="n">
-        <v>7327188</v>
+        <v>7327016</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10884,12 +10885,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10900,7 +10901,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118710620</v>
+        <v>118710618</v>
       </c>
       <c r="B101" t="n">
         <v>80467</v>
@@ -10935,10 +10936,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>694697</v>
+        <v>694712</v>
       </c>
       <c r="R101" t="n">
-        <v>7327145</v>
+        <v>7327188</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11001,7 +11002,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118712796</v>
+        <v>118710620</v>
       </c>
       <c r="B102" t="n">
         <v>80467</v>
@@ -11032,17 +11033,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>694616</v>
+        <v>694697</v>
       </c>
       <c r="R102" t="n">
-        <v>7327016</v>
+        <v>7327145</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11086,12 +11087,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11102,7 +11103,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118713513</v>
+        <v>118712796</v>
       </c>
       <c r="B103" t="n">
         <v>80467</v>
@@ -11133,14 +11134,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>694753</v>
+        <v>694616</v>
       </c>
       <c r="R103" t="n">
-        <v>7327193</v>
+        <v>7327016</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11187,12 +11188,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11203,7 +11204,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118713514</v>
+        <v>118713513</v>
       </c>
       <c r="B104" t="n">
         <v>80467</v>
@@ -11238,10 +11239,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>694657</v>
+        <v>694753</v>
       </c>
       <c r="R104" t="n">
-        <v>7327252</v>
+        <v>7327193</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11304,7 +11305,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118713515</v>
+        <v>118713514</v>
       </c>
       <c r="B105" t="n">
         <v>80467</v>
@@ -11339,10 +11340,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>694667</v>
+        <v>694657</v>
       </c>
       <c r="R105" t="n">
-        <v>7327042</v>
+        <v>7327252</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11405,7 +11406,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118713516</v>
+        <v>118713515</v>
       </c>
       <c r="B106" t="n">
         <v>80467</v>
@@ -11440,10 +11441,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>694832</v>
+        <v>694667</v>
       </c>
       <c r="R106" t="n">
-        <v>7326976</v>
+        <v>7327042</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11506,10 +11507,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134864207</v>
+        <v>118713516</v>
       </c>
       <c r="B107" t="n">
-        <v>80499</v>
+        <v>80467</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11537,14 +11538,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>694755</v>
+        <v>694832</v>
       </c>
       <c r="R107" t="n">
-        <v>7327187</v>
+        <v>7326976</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11571,12 +11572,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11587,41 +11588,30 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118710593</v>
+        <v>134864207</v>
       </c>
       <c r="B108" t="n">
-        <v>80468</v>
+        <v>80499</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11629,37 +11619,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>694653</v>
+        <v>694755</v>
       </c>
       <c r="R108" t="n">
-        <v>7327259</v>
+        <v>7327187</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11683,12 +11673,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11699,27 +11689,38 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118710596</v>
+        <v>118710593</v>
       </c>
       <c r="B109" t="n">
         <v>80468</v>
@@ -11754,10 +11755,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>694713</v>
+        <v>694653</v>
       </c>
       <c r="R109" t="n">
-        <v>7327186</v>
+        <v>7327259</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -11820,7 +11821,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118710598</v>
+        <v>118710596</v>
       </c>
       <c r="B110" t="n">
         <v>80468</v>
@@ -11855,10 +11856,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>694708</v>
+        <v>694713</v>
       </c>
       <c r="R110" t="n">
-        <v>7327141</v>
+        <v>7327186</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -11921,7 +11922,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118712792</v>
+        <v>118710598</v>
       </c>
       <c r="B111" t="n">
         <v>80468</v>
@@ -11952,17 +11953,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>694616</v>
+        <v>694708</v>
       </c>
       <c r="R111" t="n">
-        <v>7327016</v>
+        <v>7327141</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12006,12 +12007,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12022,7 +12023,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118713499</v>
+        <v>118712792</v>
       </c>
       <c r="B112" t="n">
         <v>80468</v>
@@ -12053,14 +12054,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>694753</v>
+        <v>694616</v>
       </c>
       <c r="R112" t="n">
-        <v>7327193</v>
+        <v>7327016</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12107,12 +12108,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12123,7 +12124,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118713500</v>
+        <v>118713499</v>
       </c>
       <c r="B113" t="n">
         <v>80468</v>
@@ -12158,10 +12159,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>694720</v>
+        <v>694753</v>
       </c>
       <c r="R113" t="n">
-        <v>7327209</v>
+        <v>7327193</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12224,7 +12225,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118713501</v>
+        <v>118713500</v>
       </c>
       <c r="B114" t="n">
         <v>80468</v>
@@ -12259,10 +12260,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>694655</v>
+        <v>694720</v>
       </c>
       <c r="R114" t="n">
-        <v>7327257</v>
+        <v>7327209</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12325,7 +12326,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118713502</v>
+        <v>118713501</v>
       </c>
       <c r="B115" t="n">
         <v>80468</v>
@@ -12360,10 +12361,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>694703</v>
+        <v>694655</v>
       </c>
       <c r="R115" t="n">
-        <v>7327042</v>
+        <v>7327257</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12426,7 +12427,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118713503</v>
+        <v>118713502</v>
       </c>
       <c r="B116" t="n">
         <v>80468</v>
@@ -12461,10 +12462,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>694820</v>
+        <v>694703</v>
       </c>
       <c r="R116" t="n">
-        <v>7326964</v>
+        <v>7327042</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12527,10 +12528,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>134864208</v>
+        <v>118713503</v>
       </c>
       <c r="B117" t="n">
-        <v>80500</v>
+        <v>80468</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12558,14 +12559,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>694764</v>
+        <v>694820</v>
       </c>
       <c r="R117" t="n">
-        <v>7327194</v>
+        <v>7326964</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12592,12 +12593,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12608,79 +12609,68 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr"/>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118708331</v>
+        <v>134864208</v>
       </c>
       <c r="B118" t="n">
-        <v>78334</v>
+        <v>80500</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>694666</v>
+        <v>694764</v>
       </c>
       <c r="R118" t="n">
-        <v>7327052</v>
+        <v>7327194</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12704,12 +12694,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12720,27 +12710,38 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118710622</v>
+        <v>118708331</v>
       </c>
       <c r="B119" t="n">
         <v>78334</v>
@@ -12775,13 +12776,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>694578</v>
+        <v>694666</v>
       </c>
       <c r="R119" t="n">
-        <v>7327260</v>
+        <v>7327052</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12825,12 +12826,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12841,7 +12842,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118712795</v>
+        <v>118710622</v>
       </c>
       <c r="B120" t="n">
         <v>78334</v>
@@ -12872,17 +12873,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>694796</v>
+        <v>694578</v>
       </c>
       <c r="R120" t="n">
-        <v>7327132</v>
+        <v>7327260</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12926,12 +12927,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -12942,7 +12943,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118713517</v>
+        <v>118712795</v>
       </c>
       <c r="B121" t="n">
         <v>78334</v>
@@ -12973,14 +12974,14 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>694605</v>
+        <v>694796</v>
       </c>
       <c r="R121" t="n">
-        <v>7327124</v>
+        <v>7327132</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13027,12 +13028,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13043,10 +13044,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118709463</v>
+        <v>118713517</v>
       </c>
       <c r="B122" t="n">
-        <v>57953</v>
+        <v>78334</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13054,42 +13055,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>694811</v>
+        <v>694605</v>
       </c>
       <c r="R122" t="n">
-        <v>7327033</v>
+        <v>7327124</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13124,11 +13117,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, flera träd</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -13141,22 +13129,26 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr"/>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>134864206</v>
+        <v>118709463</v>
       </c>
       <c r="B123" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13182,21 +13174,24 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>694817</v>
+        <v>694811</v>
       </c>
       <c r="R123" t="n">
-        <v>7327311</v>
+        <v>7327033</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13223,12 +13218,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, flera träd</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13243,62 +13243,62 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118734905</v>
+        <v>134864206</v>
       </c>
       <c r="B124" t="n">
-        <v>5179</v>
+        <v>57975</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>694594</v>
+        <v>694817</v>
       </c>
       <c r="R124" t="n">
-        <v>7327119</v>
+        <v>7327311</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13325,22 +13325,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13351,50 +13341,26 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL124" t="inlineStr">
-        <is>
-          <t>Klen granlåga.</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga.</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118734904</v>
+        <v>118734905</v>
       </c>
       <c r="B125" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13402,21 +13368,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13527,45 +13493,50 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118713518</v>
+        <v>118734904</v>
       </c>
       <c r="B126" t="n">
-        <v>41601</v>
+        <v>5199</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>215713</v>
+        <v>105930</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>694654</v>
+        <v>694594</v>
       </c>
       <c r="R126" t="n">
-        <v>7327049</v>
+        <v>7327119</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13595,11 +13566,21 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
@@ -13608,16 +13589,36 @@
       </c>
       <c r="AG126" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL126" t="inlineStr">
+        <is>
+          <t>Klen granlåga.</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga.</t>
+        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13628,45 +13629,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118722894</v>
+        <v>118713518</v>
       </c>
       <c r="B127" t="n">
-        <v>99022</v>
+        <v>41601</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220093</v>
+        <v>215713</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>694764</v>
+        <v>694654</v>
       </c>
       <c r="R127" t="n">
-        <v>7327023</v>
+        <v>7327049</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13713,12 +13714,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13729,10 +13730,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118712790</v>
+        <v>118722894</v>
       </c>
       <c r="B128" t="n">
-        <v>97989</v>
+        <v>99022</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13740,21 +13741,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221941</v>
+        <v>220093</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13764,10 +13765,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>694803</v>
+        <v>694764</v>
       </c>
       <c r="R128" t="n">
-        <v>7327101</v>
+        <v>7327023</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13814,12 +13815,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13830,10 +13831,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118713493</v>
+        <v>118712790</v>
       </c>
       <c r="B129" t="n">
-        <v>99140</v>
+        <v>97989</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13841,34 +13842,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>694825</v>
+        <v>694803</v>
       </c>
       <c r="R129" t="n">
-        <v>7326942</v>
+        <v>7327101</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13915,12 +13916,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -13931,7 +13932,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118722880</v>
+        <v>118713493</v>
       </c>
       <c r="B130" t="n">
         <v>99140</v>
@@ -13962,14 +13963,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>694786</v>
+        <v>694825</v>
       </c>
       <c r="R130" t="n">
-        <v>7326967</v>
+        <v>7326942</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14016,12 +14017,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14032,7 +14033,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118734906</v>
+        <v>118722880</v>
       </c>
       <c r="B131" t="n">
         <v>99140</v>
@@ -14067,10 +14068,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>694822</v>
+        <v>694786</v>
       </c>
       <c r="R131" t="n">
-        <v>7326941</v>
+        <v>7326967</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14100,19 +14101,9 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14127,12 +14118,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14143,48 +14134,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118710589</v>
+        <v>118734906</v>
       </c>
       <c r="B132" t="n">
-        <v>79085</v>
+        <v>99140</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>694651</v>
+        <v>694822</v>
       </c>
       <c r="R132" t="n">
-        <v>7327455</v>
+        <v>7326941</v>
       </c>
       <c r="S132" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14211,9 +14202,19 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14228,12 +14229,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14244,7 +14245,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118710591</v>
+        <v>118710589</v>
       </c>
       <c r="B133" t="n">
         <v>79085</v>
@@ -14279,10 +14280,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>694578</v>
+        <v>694651</v>
       </c>
       <c r="R133" t="n">
-        <v>7327260</v>
+        <v>7327455</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14345,7 +14346,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118710592</v>
+        <v>118710591</v>
       </c>
       <c r="B134" t="n">
         <v>79085</v>
@@ -14380,10 +14381,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>694844</v>
+        <v>694578</v>
       </c>
       <c r="R134" t="n">
-        <v>7327030</v>
+        <v>7327260</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14446,7 +14447,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118712791</v>
+        <v>118710592</v>
       </c>
       <c r="B135" t="n">
         <v>79085</v>
@@ -14477,17 +14478,17 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>694796</v>
+        <v>694844</v>
       </c>
       <c r="R135" t="n">
-        <v>7327132</v>
+        <v>7327030</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14531,12 +14532,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14547,7 +14548,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118713497</v>
+        <v>118712791</v>
       </c>
       <c r="B136" t="n">
         <v>79085</v>
@@ -14578,14 +14579,14 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>694577</v>
+        <v>694796</v>
       </c>
       <c r="R136" t="n">
-        <v>7327264</v>
+        <v>7327132</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14632,12 +14633,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14648,10 +14649,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134864191</v>
+        <v>118713497</v>
       </c>
       <c r="B137" t="n">
-        <v>79131</v>
+        <v>79085</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14679,14 +14680,14 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>694575</v>
+        <v>694577</v>
       </c>
       <c r="R137" t="n">
-        <v>7327243</v>
+        <v>7327264</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14713,12 +14714,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14729,41 +14730,30 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY137" t="inlineStr"/>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118710582</v>
+        <v>134864191</v>
       </c>
       <c r="B138" t="n">
-        <v>79917</v>
+        <v>79131</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14771,37 +14761,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Björnideforsen B, Pi lm</t>
+          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>694776</v>
+        <v>694575</v>
       </c>
       <c r="R138" t="n">
-        <v>7327401</v>
+        <v>7327243</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14825,12 +14815,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14841,27 +14831,38 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118710584</v>
+        <v>118710582</v>
       </c>
       <c r="B139" t="n">
         <v>79917</v>
@@ -14896,10 +14897,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>694578</v>
+        <v>694776</v>
       </c>
       <c r="R139" t="n">
-        <v>7327260</v>
+        <v>7327401</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14962,7 +14963,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118713486</v>
+        <v>118710584</v>
       </c>
       <c r="B140" t="n">
         <v>79917</v>
@@ -14997,13 +14998,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>694577</v>
+        <v>694578</v>
       </c>
       <c r="R140" t="n">
-        <v>7327264</v>
+        <v>7327260</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15047,12 +15048,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15063,7 +15064,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118713488</v>
+        <v>118713486</v>
       </c>
       <c r="B141" t="n">
         <v>79917</v>
@@ -15098,10 +15099,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>694605</v>
+        <v>694577</v>
       </c>
       <c r="R141" t="n">
-        <v>7327124</v>
+        <v>7327264</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15164,7 +15165,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118713489</v>
+        <v>118713488</v>
       </c>
       <c r="B142" t="n">
         <v>79917</v>
@@ -15199,10 +15200,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>694623</v>
+        <v>694605</v>
       </c>
       <c r="R142" t="n">
-        <v>7327061</v>
+        <v>7327124</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15265,10 +15266,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>134864192</v>
+        <v>118713489</v>
       </c>
       <c r="B143" t="n">
-        <v>79963</v>
+        <v>79917</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15296,14 +15297,14 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
+          <t>Björnideforsen B, Pi lm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>694575</v>
+        <v>694623</v>
       </c>
       <c r="R143" t="n">
-        <v>7327265</v>
+        <v>7327061</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15330,12 +15331,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15346,41 +15347,30 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr"/>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118712789</v>
+        <v>134864192</v>
       </c>
       <c r="B144" t="n">
-        <v>80341</v>
+        <v>79963</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15388,32 +15378,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6331316</v>
+        <v>229821</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Rostania effusa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>A.Košuth. et al.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Björnideforsen, Pi lm</t>
+          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>694619</v>
+        <v>694575</v>
       </c>
       <c r="R144" t="n">
-        <v>7327013</v>
+        <v>7327265</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15440,12 +15432,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15454,78 +15446,76 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>Sälgbark</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>134864205</v>
+        <v>118712789</v>
       </c>
       <c r="B145" t="n">
-        <v>91937</v>
+        <v>80341</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6331316</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rostania effusa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>A.Košuth. et al.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
+          <t>Björnideforsen, Pi lm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>694762</v>
+        <v>694619</v>
       </c>
       <c r="R145" t="n">
-        <v>7327579</v>
+        <v>7327013</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15552,12 +15542,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15566,65 +15556,65 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Sälgbark</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY145" t="inlineStr"/>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>134864204</v>
+        <v>134864205</v>
       </c>
       <c r="B146" t="n">
-        <v>78776</v>
+        <v>91937</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15634,10 +15624,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>694629</v>
+        <v>694762</v>
       </c>
       <c r="R146" t="n">
-        <v>7327607</v>
+        <v>7327579</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15711,10 +15701,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>134864202</v>
+        <v>134864204</v>
       </c>
       <c r="B147" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15722,21 +15712,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15746,10 +15736,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>694571</v>
+        <v>694629</v>
       </c>
       <c r="R147" t="n">
-        <v>7327530</v>
+        <v>7327607</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15823,10 +15813,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>134864203</v>
+        <v>134864202</v>
       </c>
       <c r="B148" t="n">
-        <v>79131</v>
+        <v>79992</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15834,21 +15824,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15858,10 +15848,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>694574</v>
+        <v>694571</v>
       </c>
       <c r="R148" t="n">
-        <v>7327527</v>
+        <v>7327530</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15932,6 +15922,118 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>134864203</v>
+      </c>
+      <c r="B149" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Trollberget, Piteälven EP, Arvidsjaur, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>694574</v>
+      </c>
+      <c r="R149" t="n">
+        <v>7327527</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
